--- a/docs/xlsx/jobs-2026-10-24.xlsx
+++ b/docs/xlsx/jobs-2026-10-24.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="46">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,127 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>Equitable Building Decarbonization (EBD) Program Advisor (Community Engagement)</t>
+  </si>
+  <si>
+    <t>The Niles Foundation</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 35.00 - 37.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Environment, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fda9f810ed29463d9654128824e447aa-equitable-building-decarbonization-ebd-program-advisor-community-engagement-the-niles-foundation-los-angeles</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>La Plaza</t>
+  </si>
+  <si>
+    <t>Palisade, Colorado</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Policy, Rural Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/8e61e02b7b7b45ec9ac5a0989f80c2f5-executive-director-la-plaza-palisade</t>
+  </si>
+  <si>
+    <t>OPPORTUNITY: ELEMENTARY CLASSROOM TEACHER: 2nd, 3rd or 4th-5th GRADE (NATIVE LEVEL OF ENGLISH PROFICIENCY REQUIRED)</t>
+  </si>
+  <si>
+    <t>Colegio Americano del Sur</t>
+  </si>
+  <si>
+    <t>Santa Lucia, Escuintla, GT</t>
+  </si>
+  <si>
+    <t>USD 18000.00 - 20000.00/year</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f674442af7444842984fd77729743fb9-opportunity-elementary-classroom-teacher-2nd-3rd-or-4th-5th-grade-native-level-of-english-proficiency-required-colegio-americano-del-sur-santa-lucia</t>
+  </si>
+  <si>
+    <t>OPPORTUNITY: HIGH LEVEL ENGLISH PROFICIENT, CERTIFIED High School English Language Arts Classroom (Teacher/Fellow) (Including school related activity involvement)</t>
+  </si>
+  <si>
+    <t>Santa Lucia, Cotzumaguapa, ES, GT</t>
+  </si>
+  <si>
+    <t>USD 1800.00 - 2000.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Conflict Resolution, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/516c685bc6554034b63d378b059de8ed-opportunity-high-level-english-proficient-certified-high-school-english-language-arts-classroom-teacherfellow-including-school-related-activity-involvement-colegio-americano-del-sur-santa-lucia-cotzumaguapa</t>
+  </si>
+  <si>
+    <t>OPPORTUNITY: Middle School Social Studies/English Classroom Teacher (High Level of English Proficiency Speaker required.)</t>
+  </si>
+  <si>
+    <t>Santa Lucia, Cotzumaguapa, ESCUINTLA, GT</t>
+  </si>
+  <si>
+    <t>Science Technology, Rural Areas, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b1e1d1285ba645119cec7e12772038fb-opportunity-middle-school-social-studiesenglish-classroom-teacher-high-level-of-english-proficiency-speaker-required-colegio-americano-del-sur-santa-lucia-cotzumaguapa</t>
+  </si>
+  <si>
+    <t>School Based Nurse - Barwaaqo University</t>
+  </si>
+  <si>
+    <t>Abaarso School of Science and Technology</t>
+  </si>
+  <si>
+    <t>Hargeisa, Woqooyi Galbeed, SO</t>
+  </si>
+  <si>
+    <t>USD 325.00 - 325.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c7b0533c8fca44588d4d82f3bc884ba2-school-based-nurse-barwaaqo-university-abaarso-school-of-science-and-technology-hargeisa</t>
+  </si>
+  <si>
+    <t>Teaching Abroad Opportunity - Abaarso School (Somaliland)</t>
+  </si>
+  <si>
+    <t>Hargeisa, Somaliland, Woqoyi Galbed, SO</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e0d18bb6f34e4b35be937d23ef2b7718-teaching-abroad-opportunity-abaarso-school-somaliland-abaarso-school-of-science-and-technology-hargeisa-somaliland</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +168,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +194,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -514,7 +633,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +672,178 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-10-24.xlsx
+++ b/docs/xlsx/jobs-2026-10-24.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="55">
   <si>
     <t>Title</t>
   </si>
@@ -40,6 +40,27 @@
     <t>Link</t>
   </si>
   <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>Museum of Craft and Design</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e81cdc91c0d445f78ae3973e4d2d4f80-director-of-development-museum-of-craft-and-design-san-francisco</t>
+  </si>
+  <si>
     <t>Equitable Building Decarbonization (EBD) Program Advisor (Community Engagement)</t>
   </si>
   <si>
@@ -49,9 +70,6 @@
     <t>Los Angeles, California</t>
   </si>
   <si>
-    <t>Full Time</t>
-  </si>
-  <si>
     <t>USD 35.00 - 37.00/hour</t>
   </si>
   <si>
@@ -77,6 +95,15 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/job/8e61e02b7b7b45ec9ac5a0989f80c2f5-executive-director-la-plaza-palisade</t>
+  </si>
+  <si>
+    <t>Major Gifts Officer</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/976f9228fc8b4ef3b1bbe14d2fef7da9-major-gifts-officer-museum-of-craft-and-design-san-francisco</t>
   </si>
   <si>
     <t>OPPORTUNITY: ELEMENTARY CLASSROOM TEACHER: 2nd, 3rd or 4th-5th GRADE (NATIVE LEVEL OF ENGLISH PROFICIENCY REQUIRED)</t>
@@ -633,7 +660,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -746,39 +773,39 @@
         <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
       </c>
       <c r="E5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="F5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
         <v>32</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>33</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
         <v>34</v>
@@ -792,45 +819,91 @@
         <v>36</v>
       </c>
       <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
         <v>37</v>
-      </c>
-      <c r="C7" t="s">
-        <v>38</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
       </c>
       <c r="E7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" t="s">
         <v>39</v>
       </c>
-      <c r="F7" t="s">
+      <c r="H7" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
         <v>42</v>
-      </c>
-      <c r="B8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" t="s">
-        <v>43</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="H8" s="2" t="s">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>45</v>
+      </c>
+      <c r="B9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -843,6 +916,8 @@
     <hyperlink ref="H6" r:id="rId5"/>
     <hyperlink ref="H7" r:id="rId6"/>
     <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
